--- a/research/traditional_assets/database/data/france/france_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/france/france_reinsurance.xlsx
@@ -588,124 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0282</v>
-      </c>
-      <c r="E2">
-        <v>-0.0572</v>
+        <v>0.0442</v>
       </c>
       <c r="F2">
-        <v>0.16</v>
+        <v>0.371</v>
       </c>
       <c r="G2">
-        <v>0.03583887524635605</v>
+        <v>0.05430053502077619</v>
       </c>
       <c r="H2">
-        <v>0.03583887524635605</v>
+        <v>0.05430053502077619</v>
       </c>
       <c r="I2">
-        <v>0.04672069812295143</v>
+        <v>-0.009163249232774775</v>
       </c>
       <c r="J2">
-        <v>0.03258968630801679</v>
+        <v>-0.009163249232774775</v>
       </c>
       <c r="K2">
-        <v>507.6</v>
+        <v>-384.4</v>
       </c>
       <c r="L2">
-        <v>0.02674873264968435</v>
+        <v>-0.02087938947883002</v>
       </c>
       <c r="M2">
-        <v>481</v>
+        <v>542.2</v>
       </c>
       <c r="N2">
-        <v>0.0834982467104121</v>
+        <v>0.132373046875</v>
       </c>
       <c r="O2">
-        <v>0.9475965327029157</v>
+        <v>-1.4105098855359</v>
       </c>
       <c r="P2">
-        <v>389.4</v>
+        <v>315.7</v>
       </c>
       <c r="Q2">
-        <v>0.06759712529944796</v>
+        <v>0.0770751953125</v>
       </c>
       <c r="R2">
-        <v>0.7671394799054373</v>
+        <v>-0.821279916753382</v>
       </c>
       <c r="S2">
-        <v>91.60000000000002</v>
+        <v>226.5000000000001</v>
       </c>
       <c r="T2">
-        <v>0.1904365904365905</v>
+        <v>0.4177425304315751</v>
       </c>
       <c r="U2">
-        <v>2998.4</v>
+        <v>1691.5</v>
       </c>
       <c r="V2">
-        <v>0.5205013366663195</v>
+        <v>0.4129638671875</v>
       </c>
       <c r="W2">
-        <v>0.06944102437823196</v>
+        <v>-0.05266979981639559</v>
       </c>
       <c r="X2">
-        <v>0.1102896584828927</v>
+        <v>0.1564583280986006</v>
       </c>
       <c r="Y2">
-        <v>-0.04084863410466077</v>
+        <v>-0.2091281279149961</v>
       </c>
       <c r="Z2">
-        <v>2.4823860291713</v>
+        <v>2.642187746666858</v>
       </c>
       <c r="AA2">
-        <v>0.08090018198609605</v>
+        <v>-0.02421102484249199</v>
       </c>
       <c r="AB2">
-        <v>0.07535303772494653</v>
+        <v>0.1064474957975272</v>
       </c>
       <c r="AC2">
-        <v>0.005547144261149523</v>
+        <v>-0.1306585206400192</v>
       </c>
       <c r="AD2">
-        <v>3690.3</v>
+        <v>3221.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3690.3</v>
+        <v>3221.2</v>
       </c>
       <c r="AG2">
-        <v>691.9000000000001</v>
+        <v>1529.7</v>
       </c>
       <c r="AH2">
-        <v>0.3904707488175729</v>
+        <v>0.4402230361340403</v>
       </c>
       <c r="AI2">
-        <v>0.3351923338934557</v>
+        <v>0.3081013868962219</v>
       </c>
       <c r="AJ2">
-        <v>0.1072297559085626</v>
+        <v>0.271912828625771</v>
       </c>
       <c r="AK2">
-        <v>0.08636766486499982</v>
+        <v>0.1745535459576653</v>
       </c>
       <c r="AL2">
-        <v>119.4</v>
+        <v>99</v>
       </c>
       <c r="AM2">
-        <v>119.4</v>
+        <v>99</v>
       </c>
       <c r="AN2">
-        <v>3.995128288405327</v>
+        <v>-58.67395264116576</v>
       </c>
       <c r="AO2">
-        <v>7.425460636515913</v>
+        <v>-1.704040404040404</v>
       </c>
       <c r="AP2">
-        <v>0.7490527227454802</v>
+        <v>-27.86338797814208</v>
       </c>
       <c r="AQ2">
-        <v>7.425460636515913</v>
+        <v>-1.704040404040404</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0282</v>
-      </c>
-      <c r="E3">
-        <v>-0.0572</v>
+        <v>0.0442</v>
       </c>
       <c r="F3">
-        <v>0.16</v>
+        <v>0.371</v>
       </c>
       <c r="G3">
-        <v>0.03583887524635605</v>
+        <v>0.05430053502077619</v>
       </c>
       <c r="H3">
-        <v>0.03583887524635605</v>
+        <v>0.05430053502077619</v>
       </c>
       <c r="I3">
-        <v>0.04672069812295143</v>
+        <v>-0.009163249232774775</v>
       </c>
       <c r="J3">
-        <v>0.03258968630801679</v>
+        <v>-0.009163249232774775</v>
       </c>
       <c r="K3">
-        <v>507.6</v>
+        <v>-384.4</v>
       </c>
       <c r="L3">
-        <v>0.02674873264968435</v>
+        <v>-0.02087938947883002</v>
       </c>
       <c r="M3">
-        <v>481</v>
+        <v>542.2</v>
       </c>
       <c r="N3">
-        <v>0.0834982467104121</v>
+        <v>0.132373046875</v>
       </c>
       <c r="O3">
-        <v>0.9475965327029157</v>
+        <v>-1.4105098855359</v>
       </c>
       <c r="P3">
-        <v>389.4</v>
+        <v>315.7</v>
       </c>
       <c r="Q3">
-        <v>0.06759712529944796</v>
+        <v>0.0770751953125</v>
       </c>
       <c r="R3">
-        <v>0.7671394799054373</v>
+        <v>-0.821279916753382</v>
       </c>
       <c r="S3">
-        <v>91.60000000000002</v>
+        <v>226.5000000000001</v>
       </c>
       <c r="T3">
-        <v>0.1904365904365905</v>
+        <v>0.4177425304315751</v>
       </c>
       <c r="U3">
-        <v>2998.4</v>
+        <v>1691.5</v>
       </c>
       <c r="V3">
-        <v>0.5205013366663195</v>
+        <v>0.4129638671875</v>
       </c>
       <c r="W3">
-        <v>0.06944102437823196</v>
+        <v>-0.05266979981639559</v>
       </c>
       <c r="X3">
-        <v>0.1102896584828927</v>
+        <v>0.1564583280986006</v>
       </c>
       <c r="Y3">
-        <v>-0.04084863410466077</v>
+        <v>-0.2091281279149961</v>
       </c>
       <c r="Z3">
-        <v>2.4823860291713</v>
+        <v>2.642187746666858</v>
       </c>
       <c r="AA3">
-        <v>0.08090018198609605</v>
+        <v>-0.02421102484249199</v>
       </c>
       <c r="AB3">
-        <v>0.07535303772494653</v>
+        <v>0.1064474957975272</v>
       </c>
       <c r="AC3">
-        <v>0.005547144261149523</v>
+        <v>-0.1306585206400192</v>
       </c>
       <c r="AD3">
-        <v>3690.3</v>
+        <v>3221.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3690.3</v>
+        <v>3221.2</v>
       </c>
       <c r="AG3">
-        <v>691.9000000000001</v>
+        <v>1529.7</v>
       </c>
       <c r="AH3">
-        <v>0.3904707488175729</v>
+        <v>0.4402230361340403</v>
       </c>
       <c r="AI3">
-        <v>0.3351923338934557</v>
+        <v>0.3081013868962219</v>
       </c>
       <c r="AJ3">
-        <v>0.1072297559085626</v>
+        <v>0.271912828625771</v>
       </c>
       <c r="AK3">
-        <v>0.08636766486499982</v>
+        <v>0.1745535459576653</v>
       </c>
       <c r="AL3">
-        <v>119.4</v>
+        <v>99</v>
       </c>
       <c r="AM3">
-        <v>119.4</v>
+        <v>99</v>
       </c>
       <c r="AN3">
-        <v>3.995128288405327</v>
+        <v>-58.67395264116576</v>
       </c>
       <c r="AO3">
-        <v>7.425460636515913</v>
+        <v>-1.704040404040404</v>
       </c>
       <c r="AP3">
-        <v>0.7490527227454802</v>
+        <v>-27.86338797814208</v>
       </c>
       <c r="AQ3">
-        <v>7.425460636515913</v>
+        <v>-1.704040404040404</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/france/france_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/france/france_reinsurance.xlsx
@@ -588,121 +588,109 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0442</v>
+        <v>0.05429999999999999</v>
+      </c>
+      <c r="E2">
+        <v>0.179</v>
       </c>
       <c r="F2">
-        <v>0.371</v>
+        <v>0.02</v>
       </c>
       <c r="G2">
-        <v>0.05430053502077619</v>
+        <v>0.001309017624650968</v>
       </c>
       <c r="H2">
-        <v>0.05430053502077619</v>
+        <v>0.001309017624650968</v>
       </c>
       <c r="I2">
-        <v>-0.009163249232774775</v>
+        <v>0.1025648269789474</v>
       </c>
       <c r="J2">
-        <v>-0.009163249232774775</v>
+        <v>0.07204754280803904</v>
       </c>
       <c r="K2">
-        <v>-384.4</v>
+        <v>1456.4</v>
       </c>
       <c r="L2">
-        <v>-0.02087938947883002</v>
+        <v>0.06857745570293776</v>
       </c>
       <c r="M2">
-        <v>542.2</v>
+        <v>281.5</v>
       </c>
       <c r="N2">
-        <v>0.132373046875</v>
+        <v>0.05363948170731708</v>
       </c>
       <c r="O2">
-        <v>-1.4105098855359</v>
+        <v>0.1932848118648723</v>
       </c>
       <c r="P2">
-        <v>315.7</v>
+        <v>266.7</v>
       </c>
       <c r="Q2">
-        <v>0.0770751953125</v>
+        <v>0.05081935975609756</v>
       </c>
       <c r="R2">
-        <v>-0.821279916753382</v>
+        <v>0.1831227684702005</v>
       </c>
       <c r="S2">
-        <v>226.5000000000001</v>
+        <v>14.80000000000001</v>
       </c>
       <c r="T2">
-        <v>0.4177425304315751</v>
+        <v>0.05257548845470697</v>
       </c>
       <c r="U2">
-        <v>1691.5</v>
+        <v>1893.5</v>
       </c>
       <c r="V2">
-        <v>0.4129638671875</v>
-      </c>
-      <c r="W2">
-        <v>-0.05266979981639559</v>
+        <v>0.3608041158536585</v>
       </c>
       <c r="X2">
-        <v>0.1564583280986006</v>
-      </c>
-      <c r="Y2">
-        <v>-0.2091281279149961</v>
-      </c>
-      <c r="Z2">
-        <v>2.642187746666858</v>
-      </c>
-      <c r="AA2">
-        <v>-0.02421102484249199</v>
+        <v>0.1237970869654566</v>
       </c>
       <c r="AB2">
-        <v>0.1064474957975272</v>
-      </c>
-      <c r="AC2">
-        <v>-0.1306585206400192</v>
+        <v>0.09062766190882615</v>
       </c>
       <c r="AD2">
-        <v>3221.2</v>
+        <v>3442</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3221.2</v>
+        <v>3442</v>
       </c>
       <c r="AG2">
-        <v>1529.7</v>
+        <v>1548.5</v>
       </c>
       <c r="AH2">
-        <v>0.4402230361340403</v>
+        <v>0.3960874568469505</v>
       </c>
       <c r="AI2">
-        <v>0.3081013868962219</v>
+        <v>0.3289844683393071</v>
       </c>
       <c r="AJ2">
-        <v>0.271912828625771</v>
+        <v>0.2278378577208857</v>
       </c>
       <c r="AK2">
-        <v>0.1745535459576653</v>
+        <v>0.1807095343680709</v>
       </c>
       <c r="AL2">
-        <v>99</v>
+        <v>133.4</v>
       </c>
       <c r="AM2">
-        <v>99</v>
+        <v>133.4</v>
       </c>
       <c r="AN2">
-        <v>-58.67395264116576</v>
+        <v>1.557677512784541</v>
       </c>
       <c r="AO2">
-        <v>-1.704040404040404</v>
+        <v>16.32833583208395</v>
       </c>
       <c r="AP2">
-        <v>-27.86338797814208</v>
+        <v>0.7007738607050732</v>
       </c>
       <c r="AQ2">
-        <v>-1.704040404040404</v>
+        <v>16.32833583208395</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +710,109 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0442</v>
+        <v>0.05429999999999999</v>
+      </c>
+      <c r="E3">
+        <v>0.179</v>
       </c>
       <c r="F3">
-        <v>0.371</v>
+        <v>0.02</v>
       </c>
       <c r="G3">
-        <v>0.05430053502077619</v>
+        <v>0.001309017624650968</v>
       </c>
       <c r="H3">
-        <v>0.05430053502077619</v>
+        <v>0.001309017624650968</v>
       </c>
       <c r="I3">
-        <v>-0.009163249232774775</v>
+        <v>0.1025648269789474</v>
       </c>
       <c r="J3">
-        <v>-0.009163249232774775</v>
+        <v>0.07204754280803904</v>
       </c>
       <c r="K3">
-        <v>-384.4</v>
+        <v>1456.4</v>
       </c>
       <c r="L3">
-        <v>-0.02087938947883002</v>
+        <v>0.06857745570293776</v>
       </c>
       <c r="M3">
-        <v>542.2</v>
+        <v>281.5</v>
       </c>
       <c r="N3">
-        <v>0.132373046875</v>
+        <v>0.05363948170731708</v>
       </c>
       <c r="O3">
-        <v>-1.4105098855359</v>
+        <v>0.1932848118648723</v>
       </c>
       <c r="P3">
-        <v>315.7</v>
+        <v>266.7</v>
       </c>
       <c r="Q3">
-        <v>0.0770751953125</v>
+        <v>0.05081935975609756</v>
       </c>
       <c r="R3">
-        <v>-0.821279916753382</v>
+        <v>0.1831227684702005</v>
       </c>
       <c r="S3">
-        <v>226.5000000000001</v>
+        <v>14.80000000000001</v>
       </c>
       <c r="T3">
-        <v>0.4177425304315751</v>
+        <v>0.05257548845470697</v>
       </c>
       <c r="U3">
-        <v>1691.5</v>
+        <v>1893.5</v>
       </c>
       <c r="V3">
-        <v>0.4129638671875</v>
-      </c>
-      <c r="W3">
-        <v>-0.05266979981639559</v>
+        <v>0.3608041158536585</v>
       </c>
       <c r="X3">
-        <v>0.1564583280986006</v>
-      </c>
-      <c r="Y3">
-        <v>-0.2091281279149961</v>
-      </c>
-      <c r="Z3">
-        <v>2.642187746666858</v>
-      </c>
-      <c r="AA3">
-        <v>-0.02421102484249199</v>
+        <v>0.1237970869654566</v>
       </c>
       <c r="AB3">
-        <v>0.1064474957975272</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1306585206400192</v>
+        <v>0.09062766190882615</v>
       </c>
       <c r="AD3">
-        <v>3221.2</v>
+        <v>3442</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3221.2</v>
+        <v>3442</v>
       </c>
       <c r="AG3">
-        <v>1529.7</v>
+        <v>1548.5</v>
       </c>
       <c r="AH3">
-        <v>0.4402230361340403</v>
+        <v>0.3960874568469505</v>
       </c>
       <c r="AI3">
-        <v>0.3081013868962219</v>
+        <v>0.3289844683393071</v>
       </c>
       <c r="AJ3">
-        <v>0.271912828625771</v>
+        <v>0.2278378577208857</v>
       </c>
       <c r="AK3">
-        <v>0.1745535459576653</v>
+        <v>0.1807095343680709</v>
       </c>
       <c r="AL3">
-        <v>99</v>
+        <v>133.4</v>
       </c>
       <c r="AM3">
-        <v>99</v>
+        <v>133.4</v>
       </c>
       <c r="AN3">
-        <v>-58.67395264116576</v>
+        <v>1.557677512784541</v>
       </c>
       <c r="AO3">
-        <v>-1.704040404040404</v>
+        <v>16.32833583208395</v>
       </c>
       <c r="AP3">
-        <v>-27.86338797814208</v>
+        <v>0.7007738607050732</v>
       </c>
       <c r="AQ3">
-        <v>-1.704040404040404</v>
+        <v>16.32833583208395</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/france/france_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/france/france_reinsurance.xlsx
@@ -588,109 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.05429999999999999</v>
-      </c>
-      <c r="E2">
-        <v>0.179</v>
+        <v>-0.006790000000000001</v>
       </c>
       <c r="F2">
-        <v>0.02</v>
+        <v>0.285</v>
       </c>
       <c r="G2">
-        <v>0.001309017624650968</v>
+        <v>0.09100930705234569</v>
       </c>
       <c r="H2">
-        <v>0.001309017624650968</v>
+        <v>0.09100930705234569</v>
       </c>
       <c r="I2">
-        <v>0.1025648269789474</v>
+        <v>0.02273079595105902</v>
       </c>
       <c r="J2">
-        <v>0.07204754280803904</v>
+        <v>0.01136539797552951</v>
       </c>
       <c r="K2">
-        <v>1456.4</v>
+        <v>-74.7</v>
       </c>
       <c r="L2">
-        <v>0.06857745570293776</v>
+        <v>-0.004288937755857816</v>
       </c>
       <c r="M2">
-        <v>281.5</v>
+        <v>406</v>
       </c>
       <c r="N2">
-        <v>0.05363948170731708</v>
+        <v>0.09263061829796942</v>
       </c>
       <c r="O2">
-        <v>0.1932848118648723</v>
+        <v>-5.435073627844712</v>
       </c>
       <c r="P2">
-        <v>266.7</v>
+        <v>358</v>
       </c>
       <c r="Q2">
-        <v>0.05081935975609756</v>
+        <v>0.08167921514944103</v>
       </c>
       <c r="R2">
-        <v>0.1831227684702005</v>
+        <v>-4.792503346720214</v>
       </c>
       <c r="S2">
-        <v>14.80000000000001</v>
+        <v>48</v>
       </c>
       <c r="T2">
-        <v>0.05257548845470697</v>
+        <v>0.1182266009852217</v>
       </c>
       <c r="U2">
-        <v>1893.5</v>
+        <v>2089</v>
       </c>
       <c r="V2">
-        <v>0.3608041158536585</v>
+        <v>0.4766141911932467</v>
+      </c>
+      <c r="W2">
+        <v>-0.01593872020824888</v>
       </c>
       <c r="X2">
-        <v>0.1237970869654566</v>
+        <v>0.1343251705064891</v>
+      </c>
+      <c r="Y2">
+        <v>-0.150263890714738</v>
+      </c>
+      <c r="Z2">
+        <v>3.285153818586492</v>
+      </c>
+      <c r="AA2">
+        <v>0.03733708055906596</v>
       </c>
       <c r="AB2">
-        <v>0.09062766190882615</v>
+        <v>0.09403048843331566</v>
+      </c>
+      <c r="AC2">
+        <v>-0.05669340787424969</v>
       </c>
       <c r="AD2">
-        <v>3442</v>
+        <v>3571.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3442</v>
+        <v>3571.3</v>
       </c>
       <c r="AG2">
-        <v>1548.5</v>
+        <v>1482.3</v>
       </c>
       <c r="AH2">
-        <v>0.3960874568469505</v>
+        <v>0.4489772827275813</v>
       </c>
       <c r="AI2">
-        <v>0.3289844683393071</v>
+        <v>0.332988344988345</v>
       </c>
       <c r="AJ2">
-        <v>0.2278378577208857</v>
+        <v>0.2527236458493172</v>
       </c>
       <c r="AK2">
-        <v>0.1807095343680709</v>
+        <v>0.1716419638721631</v>
       </c>
       <c r="AL2">
-        <v>133.4</v>
+        <v>127.1</v>
       </c>
       <c r="AM2">
-        <v>133.4</v>
+        <v>127.1</v>
       </c>
       <c r="AN2">
-        <v>1.557677512784541</v>
+        <v>7.343820686818836</v>
       </c>
       <c r="AO2">
-        <v>16.32833583208395</v>
+        <v>3.114870180959874</v>
       </c>
       <c r="AP2">
-        <v>0.7007738607050732</v>
+        <v>3.048118445404072</v>
       </c>
       <c r="AQ2">
-        <v>16.32833583208395</v>
+        <v>3.114870180959874</v>
       </c>
     </row>
     <row r="3">
@@ -710,109 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.05429999999999999</v>
-      </c>
-      <c r="E3">
-        <v>0.179</v>
+        <v>-0.006790000000000001</v>
       </c>
       <c r="F3">
-        <v>0.02</v>
+        <v>0.285</v>
       </c>
       <c r="G3">
-        <v>0.001309017624650968</v>
+        <v>0.09100930705234569</v>
       </c>
       <c r="H3">
-        <v>0.001309017624650968</v>
+        <v>0.09100930705234569</v>
       </c>
       <c r="I3">
-        <v>0.1025648269789474</v>
+        <v>0.02273079595105902</v>
       </c>
       <c r="J3">
-        <v>0.07204754280803904</v>
+        <v>0.01136539797552951</v>
       </c>
       <c r="K3">
-        <v>1456.4</v>
+        <v>-74.7</v>
       </c>
       <c r="L3">
-        <v>0.06857745570293776</v>
+        <v>-0.004288937755857816</v>
       </c>
       <c r="M3">
-        <v>281.5</v>
+        <v>406</v>
       </c>
       <c r="N3">
-        <v>0.05363948170731708</v>
+        <v>0.09263061829796942</v>
       </c>
       <c r="O3">
-        <v>0.1932848118648723</v>
+        <v>-5.435073627844712</v>
       </c>
       <c r="P3">
-        <v>266.7</v>
+        <v>358</v>
       </c>
       <c r="Q3">
-        <v>0.05081935975609756</v>
+        <v>0.08167921514944103</v>
       </c>
       <c r="R3">
-        <v>0.1831227684702005</v>
+        <v>-4.792503346720214</v>
       </c>
       <c r="S3">
-        <v>14.80000000000001</v>
+        <v>48</v>
       </c>
       <c r="T3">
-        <v>0.05257548845470697</v>
+        <v>0.1182266009852217</v>
       </c>
       <c r="U3">
-        <v>1893.5</v>
+        <v>2089</v>
       </c>
       <c r="V3">
-        <v>0.3608041158536585</v>
+        <v>0.4766141911932467</v>
+      </c>
+      <c r="W3">
+        <v>-0.01593872020824888</v>
       </c>
       <c r="X3">
-        <v>0.1237970869654566</v>
+        <v>0.1343251705064891</v>
+      </c>
+      <c r="Y3">
+        <v>-0.150263890714738</v>
+      </c>
+      <c r="Z3">
+        <v>3.285153818586492</v>
+      </c>
+      <c r="AA3">
+        <v>0.03733708055906596</v>
       </c>
       <c r="AB3">
-        <v>0.09062766190882615</v>
+        <v>0.09403048843331566</v>
+      </c>
+      <c r="AC3">
+        <v>-0.05669340787424969</v>
       </c>
       <c r="AD3">
-        <v>3442</v>
+        <v>3571.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3442</v>
+        <v>3571.3</v>
       </c>
       <c r="AG3">
-        <v>1548.5</v>
+        <v>1482.3</v>
       </c>
       <c r="AH3">
-        <v>0.3960874568469505</v>
+        <v>0.4489772827275813</v>
       </c>
       <c r="AI3">
-        <v>0.3289844683393071</v>
+        <v>0.332988344988345</v>
       </c>
       <c r="AJ3">
-        <v>0.2278378577208857</v>
+        <v>0.2527236458493172</v>
       </c>
       <c r="AK3">
-        <v>0.1807095343680709</v>
+        <v>0.1716419638721631</v>
       </c>
       <c r="AL3">
-        <v>133.4</v>
+        <v>127.1</v>
       </c>
       <c r="AM3">
-        <v>133.4</v>
+        <v>127.1</v>
       </c>
       <c r="AN3">
-        <v>1.557677512784541</v>
+        <v>7.343820686818836</v>
       </c>
       <c r="AO3">
-        <v>16.32833583208395</v>
+        <v>3.114870180959874</v>
       </c>
       <c r="AP3">
-        <v>0.7007738607050732</v>
+        <v>3.048118445404072</v>
       </c>
       <c r="AQ3">
-        <v>16.32833583208395</v>
+        <v>3.114870180959874</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/france/france_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/france/france_reinsurance.xlsx
@@ -645,10 +645,10 @@
         <v>-0.01593872020824888</v>
       </c>
       <c r="X2">
-        <v>0.1343251705064891</v>
+        <v>0.1342838283790979</v>
       </c>
       <c r="Y2">
-        <v>-0.150263890714738</v>
+        <v>-0.1502225485873468</v>
       </c>
       <c r="Z2">
         <v>3.285153818586492</v>
@@ -657,10 +657,10 @@
         <v>0.03733708055906596</v>
       </c>
       <c r="AB2">
-        <v>0.09403048843331566</v>
+        <v>0.09400770798194273</v>
       </c>
       <c r="AC2">
-        <v>-0.05669340787424969</v>
+        <v>-0.05667062742287677</v>
       </c>
       <c r="AD2">
         <v>3571.3</v>
@@ -779,10 +779,10 @@
         <v>-0.01593872020824888</v>
       </c>
       <c r="X3">
-        <v>0.1343251705064891</v>
+        <v>0.1342838283790979</v>
       </c>
       <c r="Y3">
-        <v>-0.150263890714738</v>
+        <v>-0.1502225485873468</v>
       </c>
       <c r="Z3">
         <v>3.285153818586492</v>
@@ -791,10 +791,10 @@
         <v>0.03733708055906596</v>
       </c>
       <c r="AB3">
-        <v>0.09403048843331566</v>
+        <v>0.09400770798194273</v>
       </c>
       <c r="AC3">
-        <v>-0.05669340787424969</v>
+        <v>-0.05667062742287677</v>
       </c>
       <c r="AD3">
         <v>3571.3</v>
